--- a/summer_camp_job_application_forms/004_summer_activities_staff_application_form--summer_camp_job_application_forms.xlsx
+++ b/summer_camp_job_application_forms/004_summer_activities_staff_application_form--summer_camp_job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High_School</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bachelor’s_Degree</t>
+          <t>Bachelor’s Degree</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Master’s_Degree</t>
+          <t>Master’s Degree</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30_minutes</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1_hour</t>
+          <t>1 hour</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2_hours</t>
+          <t>2 hours</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3_hours</t>
+          <t>3 hours</t>
         </is>
       </c>
     </row>
